--- a/data/modelling/clustering/smartband/df_centroids_values.xlsx
+++ b/data/modelling/clustering/smartband/df_centroids_values.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE6"/>
+  <dimension ref="A1:AD4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,124 +441,124 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>Línea</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>Modelo</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Material de la malla</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Idiomas</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Funciones del smartwatch</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Es resistente al agua</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Tamaño de la pantalla</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Con red móvil</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Con Wi-Fi</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Con GPS</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Con Bluetooth</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Sistemas operativos compatibles del smartwatch</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Es smartband</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>Con malla intercambiable</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Idiomas</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>Peso</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Accesorios incluidos</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>Funciones del smartwatch</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>Sensores</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>Capacidad de la batería</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>Duración de la batería</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>Tamaño de la pantalla</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>Tipo de pantalla</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>Resolución máxima</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>Con pantalla táctil</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>Con red móvil</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>Con Wi-Fi</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>Con GPS</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>Con Bluetooth</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>Con NFC</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>Con ranura para tarjeta SIM</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>Sistemas operativos compatibles del smartwatch</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>Es smartband</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>Profundidad máxima de resistencia al agua</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>Es resistente al agua</t>
-        </is>
-      </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>Con cámara</t>
@@ -571,92 +571,87 @@
       </c>
       <c r="AD1" s="1" t="inlineStr">
         <is>
-          <t>Incluye cargador</t>
-        </is>
-      </c>
-      <c r="AE1" s="1" t="inlineStr">
-        <is>
-          <t>Ancho de la malla</t>
+          <t>Memoria interna</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Los numero 1</t>
+          <t>Basicas</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>10312</v>
+        <v>4351</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Xiaomi</t>
+          <t>Genérica</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Mi Smart Band 6</t>
+          <t>Smartband</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
+          <t>M4</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
           <t>Silicona</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Multilenguaje</t>
+          <t>Español,Inglés</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>11.9 g</t>
+          <t>Reloj Podometro Pulsometro Kilometros Pasos Sueño</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Cable de carga magnética,Manual</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Alarma,Aplicación deportiva,Calendario,Capturador de fotos remoto,Clima,Consumo de calorías,Control de música,Control de ciclo menstrual,Cronómetro,Cuenta pasos,Distancia recorrida,Medidor de frecuencia cardíaca,Medidor de oxígeno,Monitor de</t>
+          <t>0.96 "</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Acelerómetro,Giroscopio,Sensor óptico de frecuencia cardíaca PPG</t>
+          <t>No</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>125 mAh</t>
+          <t>No</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>14 días</t>
+          <t>No</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>1.1 "</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>AMOLED</t>
+          <t>Android,iOS</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>240 px x 240 px</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -666,52 +661,52 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>25 g</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sensor óptico de frecuencia cardíaca PPG</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>90 mAh</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>2 días</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>OLED</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>320 px x 385 px</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>Android 5.0,iOS 10.0</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>50 m</t>
+          <t>No</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>1 m</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -721,137 +716,132 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="AE2" t="inlineStr">
-        <is>
-          <t>20 mm</t>
+          <t>16 MB</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Escalon debajo de nro 1</t>
+          <t>Prioridad estetica</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>20873</v>
+        <v>9295</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>X-time</t>
+          <t>Kospet</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>W26</t>
+          <t>Smartwatch</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
+          <t>DG Venus</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
           <t>Silicona</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Multilenguaje</t>
+          <t>Español</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>44 g</t>
+          <t>Consumo de calorías</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Cargador USB,Manual</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Consumo de calorías</t>
+          <t>1.3 "</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Podómetro,Termómetro</t>
+          <t>No</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>180 mAh</t>
+          <t>No</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>Android,iOS</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>11.9 g</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>Sensor óptico de frecuencia cardíaca PPG</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>200 mAh</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
           <t>7 días</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>1.75 "</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>IPS</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>LCD IPS</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
         <is>
           <t>240 px x 240 px</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>Android,iOS</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -859,114 +849,101 @@
           <t>Sí</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>50 m</t>
-        </is>
-      </c>
+      <c r="Z3" t="inlineStr"/>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
+          <t>0 m</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr"/>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t>20 mm</t>
+          <t>64 MB</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Caros y calidad baja</t>
+          <t>Las numero 1</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>9529</v>
+        <v>10138</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Genérica</t>
+          <t>Xiaomi</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Watch</t>
+          <t>Fashion</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
+          <t>Mi Smart Band 6</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
           <t>Silicona</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Español,Inglés</t>
+          <t>Multilenguaje</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>27 g</t>
+          <t>Podómetro</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Cable USB</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Aplicación deportiva,Consumo de calorías,Cuenta pasos,Distancia recorrida,Monitor de sueño,Notificaciones,Recordatorio anti sedentarismo</t>
+          <t>1.1 "</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Sensor óptico de frecuencia cardíaca PPG</t>
+          <t>No</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>200 mAh</t>
+          <t>No</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2 días</t>
+          <t>No</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>1.3 "</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>TFT IPS</t>
+          <t>Android 5.0,iOS 10.0</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>400 x 400 px</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -976,370 +953,67 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>21 g</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Acelerómetro, Giroscopio, Sensor óptico de frecuencia cardíaca PPG</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>125 mAh</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>14 días</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>AMOLED</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>240 px x 240 px</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>Android,iOS</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>1 m</t>
+          <t>No</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>50 m</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="AE4" t="inlineStr">
-        <is>
-          <t>2 cm</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="inlineStr">
-        <is>
-          <t>Los no modernos</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>5293</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Genérica</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>M4</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Plástico</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Español</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>11.9 g</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>Adaptador USB,Cable de carga magnética</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>Ritmo Cardiaco,Presion,Calorias,Notificaciones,Alarma,Sueño</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>Sensor óptico de frecuencia cardíaca PPG</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>90 mAh</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>3 días</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>0.96 "</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>Táctil</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>160x 80</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr"/>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>Android,iOS</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>0 m</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr"/>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="AD5" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="AE5" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>Baratos pero calidad acorde</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>5363</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Genérica</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>M4</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Silicona</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Español</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>27 g</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>Cable USB</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>cardio,deportes</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>Sensor óptico de frecuencia cardíaca PPG</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>90 mAh</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>2 días</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>1.3 "</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>OLED</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>160x 80</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="R6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>Android,iOS</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>0 m</t>
-        </is>
-      </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AD6" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="AE6" t="inlineStr">
-        <is>
-          <t>20 mm</t>
+          <t>32 MB</t>
         </is>
       </c>
     </row>

--- a/data/modelling/clustering/smartband/df_centroids_values.xlsx
+++ b/data/modelling/clustering/smartband/df_centroids_values.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD4"/>
+  <dimension ref="A1:AI4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,217 +441,242 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>Modelo</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Material de la malla</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Rango de ajuste de la malla</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Con malla intercambiable</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Idiomas</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Peso</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Funciones del smartwatch</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Sensores</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Capacidad de la batería</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Duración de la batería</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Tamaño de la pantalla</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Tipo de pantalla</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Resolución máxima</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>Con pantalla táctil</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>Con red móvil</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>Con Wi-Fi</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>Con GPS</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>Con Bluetooth</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>Con NFC</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>Con ranura para tarjeta SIM</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>Sistemas operativos compatibles del smartwatch</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Profundidad máxima de resistencia al agua</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>Es resistente al agua</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>Con cámara</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>Con micrófono</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>Memoria interna</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>Memoria RAM</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>Cantidad de núcleos del procesador</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>Clasificación de resistencia al agua y al polvo</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>Con reproducción de sonido</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
           <t>Línea</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Modelo</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Material de la malla</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Idiomas</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Funciones del smartwatch</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Es resistente al agua</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>Tamaño de la pantalla</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>Con red móvil</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>Con Wi-Fi</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>Con GPS</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>Con Bluetooth</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>Sistemas operativos compatibles del smartwatch</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>Es smartband</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>Con malla intercambiable</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>Peso</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>Sensores</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>Capacidad de la batería</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>Duración de la batería</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>Tipo de pantalla</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>Resolución máxima</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>Con pantalla táctil</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>Con NFC</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>Con ranura para tarjeta SIM</t>
-        </is>
-      </c>
-      <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>Profundidad máxima de resistencia al agua</t>
-        </is>
-      </c>
-      <c r="AB1" s="1" t="inlineStr">
-        <is>
-          <t>Con cámara</t>
-        </is>
-      </c>
-      <c r="AC1" s="1" t="inlineStr">
-        <is>
-          <t>Con micrófono</t>
-        </is>
-      </c>
-      <c r="AD1" s="1" t="inlineStr">
-        <is>
-          <t>Memoria interna</t>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>Nombres de los sistemas operativos</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Basicas</t>
+          <t>Los numero 1</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4351</v>
+        <v>9509</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Genérica</t>
+          <t>Xiaomi</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Smartband</t>
+          <t>Mi Smart Band 6</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>M4</t>
+          <t>Silicona</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Silicona</t>
+          <t>155 mm x 219 mm</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Español,Inglés</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Reloj Podometro Pulsometro Kilometros Pasos Sueño</t>
+          <t>Multilenguaje</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>12.8 g</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>0.96 "</t>
+          <t>Alarma,Alerta de vibración,Aplicación deportiva,Calendario,Capturador de fotos remoto,Clima,Consumo de calorías,Control de ciclo menstrual,Control de música,Cronómetro,Cuenta pasos,Desbloquear teléfono,Encuentra mi teléfono,Medidor de frecuen</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Acelerómetro,Giroscopio,Sensor óptico de frecuencia cardíaca PPG</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>125 mAh</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>14 días</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>1.56 "</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Android,iOS</t>
+          <t>AMOLED</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>152 px x 486 px</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -661,52 +686,52 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>25 g</t>
+          <t>No</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>Sensor óptico de frecuencia cardíaca PPG</t>
+          <t>No</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>90 mAh</t>
+          <t>No</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>2 días</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>OLED</t>
+          <t>No</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>320 px x 385 px</t>
+          <t>No</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>Android 10,iOS 14</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>50 m</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>1 m</t>
+          <t>No</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -716,234 +741,284 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>32 MB</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>16 MB</t>
+          <t>512 kB</t>
+        </is>
+      </c>
+      <c r="AE2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>IP68</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>Mi Band</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>FreeRTOS</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Prioridad estetica</t>
+          <t>Escalon debajo de numero 1</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>9295</v>
+        <v>9927</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Kospet</t>
+          <t>Belmotec</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Smartwatch</t>
+          <t>C5BLK</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>DG Venus</t>
+          <t>Silicona</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Silicona</t>
+          <t>19 - 13</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
           <t>Español</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>Consumo de calorías</t>
-        </is>
-      </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>25 g</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
+          <t>Reloj Podometro Pulsometro Kilometros Pasos Sueño</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Sensor óptico de frecuencia cardíaca PPG</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>180 mAh</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>7 días</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
           <t>1.3 "</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
       <c r="O3" t="inlineStr">
         <is>
+          <t>TFT</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>240 px x 240 px</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
           <t>Android,iOS</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>11.9 g</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>Sensor óptico de frecuencia cardíaca PPG</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>200 mAh</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>7 días</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>LCD IPS</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>240 px x 240 px</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr"/>
+          <t>1 m</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>0 m</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr"/>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>16 MB</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>64 MB</t>
+          <t>64 kB</t>
+        </is>
+      </c>
+      <c r="AE3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>IP68</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Y9</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Wear OS</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Las numero 1</t>
+          <t>Baratos pero calidad acorde</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>10138</v>
+        <v>4306</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Xiaomi</t>
+          <t>Genérica</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Fashion</t>
+          <t>M4</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Mi Smart Band 6</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
           <t>Silicona</t>
         </is>
       </c>
+      <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Multilenguaje</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Podómetro</t>
+          <t>Español</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>55 g</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>1.1 "</t>
+          <t>Alarma,Cronómetro,Giroscopio,Monitor de ritmo cardíaco,Consumo de calorías,Monitoreo de oxígeno en sangre,Obturador de cámara remota para su teléfono,Distancia de ejercicio,Admite recordatorio de llamadas y recordatorio de mensajes</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sensor óptico de frecuencia cardíaca PPG</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>90 mAh</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>3 días</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>0.96 "</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Android 5.0,iOS 10.0</t>
+          <t>LCD</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>160 px x 80 px</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -953,42 +1028,42 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>21 g</t>
+          <t>No</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>Acelerómetro, Giroscopio, Sensor óptico de frecuencia cardíaca PPG</t>
+          <t>No</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>125 mAh</t>
+          <t>No</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>14 días</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>AMOLED</t>
+          <t>No</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>240 px x 240 px</t>
+          <t>No</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>Android,iOS</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>0 m</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -998,7 +1073,7 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>50 m</t>
+          <t>No</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1008,14 +1083,27 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>128 MB</t>
         </is>
       </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>32 MB</t>
-        </is>
-      </c>
+          <t>1 GB</t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr"/>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>IP68</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr"/>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Smartband</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/modelling/clustering/smartband/df_centroids_values.xlsx
+++ b/data/modelling/clustering/smartband/df_centroids_values.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI4"/>
+  <dimension ref="A1:AF4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,173 +441,158 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>Línea</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>Modelo</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Con red móvil</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Con Wi-Fi</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Con GPS</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Con Bluetooth</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Sistemas operativos compatibles del smartwatch</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Es smartband</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Clasificación de resistencia al agua y al polvo</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Capacidad de la batería</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Duración de la batería</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Tamaño de la pantalla</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Tipo de pantalla</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>Resolución máxima</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>Material de la malla</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Rango de ajuste de la malla</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>Sensores</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>Memoria RAM</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>Profundidad máxima de resistencia al agua</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>Es resistente al agua</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>Con malla intercambiable</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>Idiomas</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>Peso</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>Funciones del smartwatch</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>Sensores</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>Capacidad de la batería</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>Duración de la batería</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>Tamaño de la pantalla</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>Tipo de pantalla</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>Resolución máxima</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>Con pantalla táctil</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>Con red móvil</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>Con Wi-Fi</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>Con GPS</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>Con Bluetooth</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>Con NFC</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>Con ranura para tarjeta SIM</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>Sistemas operativos compatibles del smartwatch</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>Profundidad máxima de resistencia al agua</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>Es resistente al agua</t>
-        </is>
-      </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>Con cámara</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>Con micrófono</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>Memoria interna</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
-        <is>
-          <t>Memoria RAM</t>
-        </is>
-      </c>
-      <c r="AE1" s="1" t="inlineStr">
-        <is>
-          <t>Cantidad de núcleos del procesador</t>
-        </is>
-      </c>
       <c r="AF1" s="1" t="inlineStr">
         <is>
-          <t>Clasificación de resistencia al agua y al polvo</t>
-        </is>
-      </c>
-      <c r="AG1" s="1" t="inlineStr">
-        <is>
           <t>Con reproducción de sonido</t>
-        </is>
-      </c>
-      <c r="AH1" s="1" t="inlineStr">
-        <is>
-          <t>Línea</t>
-        </is>
-      </c>
-      <c r="AI1" s="1" t="inlineStr">
-        <is>
-          <t>Nombres de los sistemas operativos</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Los numero 1</t>
+          <t>Mejor calidad</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>9509</v>
+        <v>13062</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -616,122 +601,122 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Mi Smart Band 6</t>
+          <t>Fashion</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
+          <t>Mi Smart Band 7</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Android 5.0, iOS 10.0</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>IP68</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>125 mAh</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>14 días</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>1.1 "</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>AMOLED</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>240 px x 240 px</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
           <t>Silicona</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>155 mm x 219 mm</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>Acelerómetro, Giroscopio, Sensor óptico de frecuencia cardíaca PPG</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>512 kB</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>50 m</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
         <is>
           <t>Multilenguaje</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>12.8 g</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>Alarma,Alerta de vibración,Aplicación deportiva,Calendario,Capturador de fotos remoto,Clima,Consumo de calorías,Control de ciclo menstrual,Control de música,Cronómetro,Cuenta pasos,Desbloquear teléfono,Encuentra mi teléfono,Medidor de frecuen</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>Acelerómetro,Giroscopio,Sensor óptico de frecuencia cardíaca PPG</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>125 mAh</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>14 días</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>1.56 "</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>AMOLED</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>152 px x 486 px</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>Android 10,iOS 14</t>
-        </is>
-      </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>50 m</t>
+          <t>54 g</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>Alarma, Alerta de vibración, Aplicación deportiva, Asistente virtual, Brújula, Calendario, Capturador de fotos remoto, Clima, Consumo de calorías, Control de ciclo menstrual, Control de música, Cronómetro, Cuenta pasos, Distancia recorrida, Encuentra mi teléfono, Medidor de frecuencia cardíaca, Medidor de oxígeno, Monitor de sueño, Notificaciones, Recibir mensajes, Recordatorio anti sedentarismo, Recordatorios, Redes sociales, Relajación, Temporizador, Velocidad, Visualizar llamadas</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -741,219 +726,189 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>32 MB</t>
+          <t>No</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>512 kB</t>
-        </is>
-      </c>
-      <c r="AE2" t="n">
-        <v>2</v>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>16 MB</t>
+        </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>IP68</t>
-        </is>
-      </c>
-      <c r="AG2" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>Mi Band</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>FreeRTOS</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Escalon debajo de numero 1</t>
+          <t>Calidad media</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>9927</v>
+        <v>9247</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Belmotec</t>
+          <t>Genérica</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>C5BLK</t>
+          <t>Smartwatch</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
+          <t>W26</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Android,iOS</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>IP68</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>200 mAh</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>7 días</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>1.75 "</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>LCD IPS</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>240 px x 240 px</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
           <t>Silicona</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>19 - 13</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>Sensor óptico de frecuencia cardíaca PPG</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>64 kB</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>0 m</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
         <is>
           <t>Español</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>25 g</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>Reloj Podometro Pulsometro Kilometros Pasos Sueño</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>Sensor óptico de frecuencia cardíaca PPG</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>180 mAh</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>7 días</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>1.3 "</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>TFT</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>240 px x 240 px</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>Android,iOS</t>
-        </is>
-      </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>1 m</t>
+          <t>27 g</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>Alarma,Aplicación deportiva,Calendario,Consumo de calorías,Cuenta pasos,Distancia recorrida,Medidor de presión arterial,Monitor de sueño,Notificaciones,Recibir mensajes,Redes sociales,Visualizar llamadas</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>16 MB</t>
-        </is>
-      </c>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>64 kB</t>
-        </is>
-      </c>
-      <c r="AE3" t="n">
-        <v>2</v>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>128 MB</t>
+        </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>IP68</t>
-        </is>
-      </c>
-      <c r="AG3" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>Y9</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>Wear OS</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Baratos pero calidad acorde</t>
+          <t>Baja calidad</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4306</v>
+        <v>6904</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -962,118 +917,122 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>M4</t>
+          <t>Smartband</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
+          <t>D20</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Android,iOS</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>IP67</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>90 mAh</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>7 días</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>0.96 "</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>LCD</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>160 px x 80 px</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
           <t>Silicona</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>Sensor óptico de frecuencia cardíaca PPG</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>0 GB</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>1 m</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
         <is>
           <t>Español</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>55 g</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>Alarma,Cronómetro,Giroscopio,Monitor de ritmo cardíaco,Consumo de calorías,Monitoreo de oxígeno en sangre,Obturador de cámara remota para su teléfono,Distancia de ejercicio,Admite recordatorio de llamadas y recordatorio de mensajes</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>Sensor óptico de frecuencia cardíaca PPG</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>90 mAh</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>3 días</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>0.96 "</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>LCD</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>160 px x 80 px</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>Android,iOS</t>
-        </is>
-      </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>0 m</t>
+          <t>25 g</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Consumo de calorías</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1083,27 +1042,24 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
           <t>128 MB</t>
         </is>
       </c>
-      <c r="AD4" t="inlineStr">
-        <is>
-          <t>1 GB</t>
-        </is>
-      </c>
-      <c r="AE4" t="inlineStr"/>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>IP68</t>
-        </is>
-      </c>
-      <c r="AG4" t="inlineStr"/>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>Smartband</t>
-        </is>
-      </c>
-      <c r="AI4" t="inlineStr"/>
+          <t>Sí</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
